--- a/out/Attention-mamba2_repeat_5_000002.xlsx
+++ b/out/Attention-mamba2_repeat_5_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000002.xlsx
+++ b/out/Attention-mamba2_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000002.xlsx
+++ b/out/Attention-mamba2_repeat_5_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.4287393093109131</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3947137892246246</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.3774135410785675</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.3637389540672302</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.389479398727417</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3687015175819397</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.3616612553596497</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.4286018013954163</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.32371786236763</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.3327444493770599</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.292087584733963</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2786866128444672</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.3052002787590027</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2866592407226562</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.2828261256217957</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2900450527667999</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2962456941604614</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2912628352642059</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.2843045294284821</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.2894507348537445</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.2946982681751251</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2830032408237457</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.3010563850402832</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.3295044898986816</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.3381863236427307</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.3201659917831421</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.318772166967392</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.3057622909545898</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2878447771072388</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2852872312068939</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2920423746109009</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2804082036018372</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.285514771938324</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.2954845130443573</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3267890214920044</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.3356971740722656</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3334817290306091</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.3351418077945709</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.3530771732330322</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.3327934145927429</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.2528992891311646</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1739007234573364</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.1347572207450867</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.1706550419330597</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1540359854698181</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1433439552783966</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.1134819760918617</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.1009513959288597</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.07111822813749313</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.1171587035059929</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.1307263970375061</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1522553563117981</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.1126560643315315</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.09832488745450974</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0935017392039299</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.1010096594691277</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.08409883826971054</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.07319092005491257</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.08503120392560959</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.07860416918992996</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.1084275916218758</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0995999351143837</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.09505202621221542</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.06629154831171036</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1065171882510185</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.1094655767083168</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.1361399590969086</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.1078945472836494</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.102803997695446</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.09782306104898453</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0992995873093605</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.08839868754148483</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.09185855835676193</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.09507369250059128</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.05096707493066788</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.05611095577478409</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.07925134152173996</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.06538372486829758</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.05394633859395981</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.06185581535100937</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.05756226927042007</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.08656450361013412</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.05661093443632126</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.06716614216566086</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.06822792440652847</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.04123514145612717</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.07389550656080246</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.08014699071645737</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.09316582232713699</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.08811422437429428</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.06090042740106583</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.1013058349490166</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0679224357008934</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0554034635424614</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.03780829161405563</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.1007160171866417</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.05882378667593002</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0669839158654213</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.04621458798646927</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.08773929625749588</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.04199319332838058</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.05898786336183548</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.07405442744493484</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.05447601526975632</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.06605436652898788</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.06452768296003342</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.05595257133245468</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.05098196119070053</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.06298960000276566</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.04500170797109604</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.07755600661039352</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.05405604094266891</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.06655629724264145</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.05377735942602158</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.06184043735265732</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.09858783334493637</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.09709460288286209</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.09634310752153397</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.1176373288035393</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.1048993393778801</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.1145826205611229</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.09016577154397964</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.09937522560358047</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.08163290470838547</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.1122114732861519</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000002.xlsx
+++ b/out/Attention-mamba2_repeat_5_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.4287393093109131</v>
+        <v>-0.4287391901016235</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3947137892246246</v>
+        <v>-0.3947135508060455</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.3774135410785675</v>
+        <v>-0.3774135112762451</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.3637389540672302</v>
+        <v>-0.3637388050556183</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.389479398727417</v>
+        <v>-0.3894792497158051</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3687015175819397</v>
+        <v>-0.3687012791633606</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.3616612553596497</v>
+        <v>-0.3616611659526825</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.4286018013954163</v>
+        <v>-0.4286015033721924</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.32371786236763</v>
+        <v>-0.323717474937439</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.3327444493770599</v>
+        <v>-0.3327442407608032</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.292087584733963</v>
+        <v>-0.2920874059200287</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2786866128444672</v>
+        <v>-0.2786864042282104</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.3052002787590027</v>
+        <v>-0.3052001595497131</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2866592407226562</v>
+        <v>-0.2866590321063995</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.2828261256217957</v>
+        <v>-0.2828260064125061</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2900450527667999</v>
+        <v>-0.2900448143482208</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2962456941604614</v>
+        <v>-0.2962455451488495</v>
       </c>
       <c r="JB18" t="n">
         <v>0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2912628352642059</v>
+        <v>-0.291262686252594</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.2843045294284821</v>
+        <v>-0.2843043804168701</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.2894507348537445</v>
+        <v>-0.289450466632843</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.2946982681751251</v>
+        <v>-0.294698029756546</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2830032408237457</v>
+        <v>-0.2830030024051666</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.3010563850402832</v>
+        <v>-0.3010563254356384</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.3295044898986816</v>
+        <v>-0.3295041918754578</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.3381863236427307</v>
+        <v>-0.3381861448287964</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.3201659917831421</v>
+        <v>-0.3201657831668854</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.318772166967392</v>
+        <v>-0.3187721371650696</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.3057622909545898</v>
+        <v>-0.3057620823383331</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2878447771072388</v>
+        <v>-0.2878446280956268</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2852872312068939</v>
+        <v>-0.2852870523929596</v>
       </c>
       <c r="JB31" t="n">
         <v>0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2920423746109009</v>
+        <v>-0.2920421957969666</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2804082036018372</v>
+        <v>-0.2804079651832581</v>
       </c>
       <c r="JB33" t="n">
         <v>0.8599999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.285514771938324</v>
+        <v>-0.285514622926712</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.2954845130443573</v>
+        <v>-0.2954843640327454</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3267890214920044</v>
+        <v>-0.3267888724803925</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.3356971740722656</v>
+        <v>-0.3356970250606537</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3334817290306091</v>
+        <v>-0.3334814012050629</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.3351418077945709</v>
+        <v>-0.3351415991783142</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.3530771732330322</v>
+        <v>-0.353076845407486</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.3327934145927429</v>
+        <v>-0.3327932357788086</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.2528992891311646</v>
+        <v>-0.2528991401195526</v>
       </c>
       <c r="JB42" t="n">
         <v>0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.1739007234573364</v>
+        <v>-0.1739005744457245</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.1347572207450867</v>
+        <v>-0.1347570419311523</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.1706550419330597</v>
+        <v>-0.1706547439098358</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1540359854698181</v>
+        <v>-0.1540357768535614</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.1433439552783966</v>
+        <v>-0.1433437466621399</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.1134819760918617</v>
+        <v>-0.1134817227721214</v>
       </c>
       <c r="JB48" t="n">
         <v>0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.1009513959288597</v>
+        <v>-0.1009509786963463</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.07111822813749313</v>
+        <v>-0.07111794501543045</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.1171587035059929</v>
+        <v>-0.1171584650874138</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.1307263970375061</v>
+        <v>-0.1307261288166046</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.1522553563117981</v>
+        <v>-0.1522547006607056</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.1126560643315315</v>
+        <v>-0.1126557365059853</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.09832488745450974</v>
+        <v>-0.09832454472780228</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0935017392039299</v>
+        <v>-0.09350153058767319</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.1010096594691277</v>
+        <v>-0.1010093316435814</v>
       </c>
       <c r="JB57" t="n">
         <v>0.2599999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.08409883826971054</v>
+        <v>-0.08409862965345383</v>
       </c>
       <c r="JB58" t="n">
         <v>0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.07319092005491257</v>
+        <v>-0.07319056242704391</v>
       </c>
       <c r="JB59" t="n">
         <v>0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.08503120392560959</v>
+        <v>-0.08503087610006332</v>
       </c>
       <c r="JB60" t="n">
         <v>0.8599999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.07860416918992996</v>
+        <v>-0.07860376685857773</v>
       </c>
       <c r="JB61" t="n">
         <v>0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.1084275916218758</v>
+        <v>-0.1084272190928459</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0995999351143837</v>
+        <v>-0.09959960728883743</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.09505202621221542</v>
+        <v>-0.09505178779363632</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.16</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.06629154831171036</v>
+        <v>-0.06629123538732529</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.16</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.1065171882510185</v>
+        <v>-0.1065166220068932</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.1094655767083168</v>
+        <v>-0.1094652786850929</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.1361399590969086</v>
+        <v>-0.1361399292945862</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.1078945472836494</v>
+        <v>-0.107894279062748</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.102803997695446</v>
+        <v>-0.1028036251664162</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.09782306104898453</v>
+        <v>-0.0978228822350502</v>
       </c>
       <c r="JB71" t="n">
         <v>0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0992995873093605</v>
+        <v>-0.09929933398962021</v>
       </c>
       <c r="JB72" t="n">
         <v>0.8599999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.08839868754148483</v>
+        <v>-0.08839853852987289</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.09185855835676193</v>
+        <v>-0.09185834974050522</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.09507369250059128</v>
+        <v>-0.09507345408201218</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.05096707493066788</v>
+        <v>-0.05096700042486191</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.05611095577478409</v>
+        <v>-0.05611091107130051</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.07925134152173996</v>
+        <v>-0.0792512521147728</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.06538372486829758</v>
+        <v>-0.06538353115320206</v>
       </c>
       <c r="JB79" t="n">
         <v>0.8599999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.05394633859395981</v>
+        <v>-0.05394624918699265</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.06185581535100937</v>
+        <v>-0.06185571104288101</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.05756226927042007</v>
+        <v>-0.05756210535764694</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.08656450361013412</v>
+        <v>-0.08656435459852219</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.05661093443632126</v>
+        <v>-0.05661078542470932</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.06716614216566086</v>
+        <v>-0.06716608256101608</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.06822792440652847</v>
+        <v>-0.06822790950536728</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.04123514145612717</v>
+        <v>-0.04123509675264359</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.02000000000000007</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.07389550656080246</v>
+        <v>-0.0738954022526741</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.16</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.08014699071645737</v>
+        <v>-0.08014673739671707</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.09316582232713699</v>
+        <v>-0.09316553920507431</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.08811422437429428</v>
+        <v>-0.08811404556035995</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.06090042740106583</v>
+        <v>-0.06090026348829269</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.1013058349490166</v>
+        <v>-0.1013056263327599</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.1600000000000001</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0679224357008934</v>
+        <v>-0.06792234629392624</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0554034635424614</v>
+        <v>-0.05540340393781662</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.03780829161405563</v>
+        <v>-0.03780829906463623</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.1007160171866417</v>
+        <v>-0.1007157191634178</v>
       </c>
       <c r="JB97" t="n">
         <v>0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.05882378667593002</v>
+        <v>-0.05882368236780167</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0669839158654213</v>
+        <v>-0.06698378175497055</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.04621458798646927</v>
+        <v>-0.0462145134806633</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.08773929625749588</v>
+        <v>-0.08773922175168991</v>
       </c>
       <c r="JB101" t="n">
         <v>0.5799999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.04199319332838058</v>
+        <v>-0.04199311882257462</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.05898786336183548</v>
+        <v>-0.05898787826299667</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.07405442744493484</v>
+        <v>-0.07405433803796768</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.05447601526975632</v>
+        <v>-0.05447595566511154</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.06605436652898788</v>
+        <v>-0.06605430692434311</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.06452768296003342</v>
+        <v>-0.06452760845422745</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.02000000000000007</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.05595257133245468</v>
+        <v>-0.05595251172780991</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.05098196119070053</v>
+        <v>-0.05098185688257217</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.06298960000276566</v>
+        <v>-0.0629894956946373</v>
       </c>
       <c r="JB110" t="n">
         <v>0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.04500170797109604</v>
+        <v>-0.04500163346529007</v>
       </c>
       <c r="JB111" t="n">
         <v>0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.07755600661039352</v>
+        <v>-0.07755584269762039</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.05405604094266891</v>
+        <v>-0.05405595153570175</v>
       </c>
       <c r="JB113" t="n">
         <v>0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.06655629724264145</v>
+        <v>-0.0665561780333519</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.16</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.05377735942602158</v>
+        <v>-0.0537772998213768</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.06184043735265732</v>
+        <v>-0.06184034794569016</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.09858783334493637</v>
+        <v>-0.09858756512403488</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.09709460288286209</v>
+        <v>-0.09709427505731583</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.09634310752153397</v>
+        <v>-0.09634273499250412</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.1176373288035393</v>
+        <v>-0.1176370605826378</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.1048993393778801</v>
+        <v>-0.1048990413546562</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.1145826205611229</v>
+        <v>-0.1145823523402214</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.09016577154397964</v>
+        <v>-0.09016559273004532</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.09937522560358047</v>
+        <v>-0.09937497228384018</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.08163290470838547</v>
+        <v>-0.08163265138864517</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.1122114732861519</v>
+        <v>-0.1122112050652504</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.9999999999999996</v>
